--- a/history.xlsx
+++ b/history.xlsx
@@ -391,7 +391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,60 @@
         <v>2000</v>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kola</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Kola</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tovoq</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>piece</t>
         </is>
@@ -463,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +578,24 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kola</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
